--- a/Outputs/PtX_demand_CZ.xlsx
+++ b/Outputs/PtX_demand_CZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,55 +488,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002636834777673857</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0005210937701778214</v>
-      </c>
+        <v>0.006662813784368281</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.01187256154201492</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00193220478741412</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>4.679537878854075e-10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0002430991954532751</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2030</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>9.701819216868525e-05</v>
-      </c>
+      <c r="C3" t="n">
+        <v>0.002636834777673857</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0005210937701778214</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>4.679537878854075e-10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0002430991954532751</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -544,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.001711240593102564</v>
+        <v>9.701819216868525e-05</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -557,14 +561,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2030</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.001711240593102564</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -576,7 +582,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -584,24 +590,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.001874926180354666</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0001697816373739507</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>6.068563423464417e-05</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -609,14 +609,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.001874926180354666</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0020067734328618</v>
+        <v>0.0001697816373739507</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.0002074940424132762</v>
+        <v>6.068563423464417e-05</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -624,7 +626,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -633,17 +635,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0020067734328618</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.0002074940424132762</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -652,29 +658,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.009704199855958301</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0001947674719947</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001277186641834586</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.009590381865822301</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.000313728971853</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.596162336022546e-06</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -684,28 +678,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.09488339522763531</v>
+        <v>0.009704199855958301</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001371690190649</v>
+        <v>0.0001947674719947</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01167223281399252</v>
+        <v>0.001277186641834586</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0619264257483374</v>
+        <v>0.009590381865822301</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0018990021266557</v>
+        <v>0.000313728971853</v>
       </c>
       <c r="K10" t="n">
-        <v>1.141145544782768e-05</v>
+        <v>1.596162336022546e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -713,20 +707,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.00639754447043152</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.09488339522763531</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001371690190649</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01167223281399252</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0619264257483374</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0018990021266557</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.141145544782768e-05</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -735,7 +739,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0006561175519646474</v>
+        <v>0.00639754447043152</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -747,102 +751,104 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002636834777673857</v>
+        <v>0.02373151299906471</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001808258785271249</v>
+        <v>8.952838470577263e-20</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008928588202750833</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.1072852439240072</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0015664576626437</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0129494199237809</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.0720280864862609</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0022127310985087</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.300761778385023e-05</v>
-      </c>
+        <v>0.02277939359087382</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.009979350073333344</v>
-      </c>
+        <v>2030</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0024972646234169</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.0006561175519646474</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>3.917290063196409e-08</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0003806931026713</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.03303116156110684</v>
+      </c>
       <c r="D15" t="n">
-        <v>9.843920302169559e-05</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>0.01368082032728617</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.03364018658103878</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1072852439240072</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0015664576626437</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0129494199237809</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0720280864862609</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0022127310985087</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.300761778385023e-05</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.006143447100847251</v>
+      </c>
       <c r="D16" t="n">
-        <v>0.001736304876414324</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>0.0117591176906101</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.001958155357646442</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -853,22 +859,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2040</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>0.009979350073333344</v>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>9.252752796519075e-10</v>
+        <v>0.0024972646234169</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>3.917290063196409e-08</v>
+      </c>
       <c r="I17" t="n">
-        <v>1.296002164840976e-10</v>
+        <v>0.0003806931026713</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -876,55 +886,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2040</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.007474128760514786</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0002061326160381924</v>
-      </c>
+      <c r="D18" t="n">
+        <v>9.843920302169559e-05</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>8.946786981804565e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2040</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.001736304876414324</v>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0010960988503425</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0.0002238464381885972</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -933,17 +937,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>9.252752796519075e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1.296002164840976e-10</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -951,30 +959,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.007474128760514786</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.0043795341426325</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0003175031110819</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.00155497867884227</v>
-      </c>
+        <v>0.0002061326160381924</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0065219019431024</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0003811297831029</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.096097011510452e-06</v>
-      </c>
+        <v>8.946786981804565e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -984,28 +986,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.0270882932946468</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.001474643217016</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.01100481732831053</v>
-      </c>
+        <v>0.0010960988503425</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.02854306645396</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0016851944930805</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.006854884539204e-05</v>
-      </c>
+        <v>0.0002238464381885972</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1013,9 +1007,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.006453919863473069</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1026,7 +1018,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1034,94 +1026,94 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.002608811033368257</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.0043795341426325</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0003175031110819</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00155497867884227</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0065219019431024</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0003811297831029</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.096097011510452e-06</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2040</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.009979350073333344</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.001834744079436019</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.01653685965735611</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.03526732445235217</v>
+        <v>0.0270882932946468</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0017921463280979</v>
+        <v>0.001474643217016</v>
       </c>
       <c r="H25" t="n">
-        <v>0.01255983518005343</v>
+        <v>0.01100481732831053</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03575897593734056</v>
+        <v>0.02854306645396</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0020663242761834</v>
+        <v>0.0016851944930805</v>
       </c>
       <c r="K25" t="n">
-        <v>1.216464585690249e-05</v>
+        <v>1.006854884539204e-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.02331652046354969</v>
-      </c>
+        <v>2040</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0034670938306759</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.006453919863473069</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>6.639491125692976e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0006131830468041</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
-        <v>0.0001000722509256611</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.01496902511000001</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.01512440969082456</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1132,17 +1124,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>0.001765109142926401</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.002608811033368257</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1153,70 +1145,88 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.03109182228418061</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01359386177004612</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.03361942470582711</v>
+      </c>
       <c r="F29" t="n">
-        <v>9.588086302009341e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.03526732445235217</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0017921463280979</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.01255983518005343</v>
+      </c>
       <c r="I29" t="n">
-        <v>4.224866691896118e-09</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.03575897593734056</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0020663242761834</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.216464585690249e-05</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.005546582782663666</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01162874624174894</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.01861181823029339</v>
-      </c>
-      <c r="F30" t="n">
-        <v>3.655514244239956e-05</v>
-      </c>
+        <v>0.00198797815895357</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>2.461079464705437e-05</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2050</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>0.02331652046354969</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>7.344238361320249e-05</v>
+        <v>0.0034670938306759</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>6.639491125692976e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>7.789809888854212e-05</v>
+        <v>0.0006131830468041</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1224,69 +1234,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2050</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0.0001000722509256611</v>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>4.05766819302163e-11</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.169192348961319e-11</v>
-      </c>
-      <c r="H32" t="n">
-        <v>5.989385138145736e-11</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.016926863433363e-10</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.61029145545919e-12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.531084594319585e-13</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2050</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.001765109142926401</v>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0005809265804677798</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0005673223150293001</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.002036920338936632</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0016966448313037</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0004901932549159</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.846703482423101e-06</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1296,28 +1286,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0025018970452341</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0013300657300867</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.009979138206718429</v>
-      </c>
+        <v>9.588086302009341e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0049884678431902</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0014505326724771</v>
-      </c>
-      <c r="K34" t="n">
-        <v>8.263855420265018e-06</v>
-      </c>
+        <v>4.224866691896118e-09</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1326,19 +1308,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.006518820299633993</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.01861181823029339</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.655514244239956e-05</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>2.461079464705437e-05</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1346,50 +1332,208 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.006476976186687356</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>7.344238361320249e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>7.789809888854212e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2050</v>
       </c>
-      <c r="C37" t="n">
-        <v>0.02331652046354969</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.001865181393852062</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.03160761471661475</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>4.05766819302163e-11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.169192348961319e-11</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.989385138145736e-11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.016926863433363e-10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.61029145545919e-12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.531084594319585e-13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0005809265804677798</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0005673223150293001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.002036920338936632</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0016966448313037</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0004901932549159</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.846703482423101e-06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0025018970452341</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0013300657300867</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.009979138206718429</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0049884678431902</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0014505326724771</v>
+      </c>
+      <c r="K39" t="n">
+        <v>8.263855420265018e-06</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.006518820299633993</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>2.046363078989088e-19</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.006476976186687356</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.02886310324621336</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.013493927635601</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.03359559287556831</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.006659924611096365</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.001897388056807923</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.01201612500046017</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.007400808941392975</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.001940725930003292</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>1.111055925579658e-05</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_CZ.xlsx
+++ b/Outputs/PtX_demand_CZ.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.00193220478741412</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.01133895372074527</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0078867012569355</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.004105922140507</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0028430581042284</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -730,16 +738,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2030</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>0.02373151299906471</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8.952838470577263e-20</v>
+      </c>
       <c r="E12" t="n">
-        <v>0.00639754447043152</v>
+        <v>0.02277939359087382</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -751,20 +763,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.02373151299906471</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.952838470577263e-20</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.02277939359087382</v>
+        <v>0.00639754447043152</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -807,25 +815,25 @@
         <v>0.03303116156110684</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01368082032728617</v>
+        <v>0.01368082032728616</v>
       </c>
       <c r="E15" t="n">
         <v>0.03364018658103878</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1072852439240072</v>
+        <v>0.1186241976447525</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0015664576626437</v>
+        <v>0.009453158919579201</v>
       </c>
       <c r="H15" t="n">
         <v>0.0129494199237809</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0720280864862609</v>
+        <v>0.07613400862676789</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0022127310985087</v>
+        <v>0.005055789202737099</v>
       </c>
       <c r="K15" t="n">
         <v>1.300761778385023e-05</v>
@@ -849,11 +857,19 @@
       <c r="E16" t="n">
         <v>0.001958155357646442</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.0323272125059983</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0092557713674598</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0154389719268968</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0028039159816962</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1080,16 +1096,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2040</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>0.01496902511000001</v>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.006453919863473069</v>
+        <v>0.01512440969082456</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1101,18 +1119,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2040</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.01496902511000001</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.01512440969082456</v>
+        <v>0.006453919863473069</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1161,19 +1177,19 @@
         <v>0.03361942470582711</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03526732445235217</v>
+        <v>0.06759453695835047</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0017921463280979</v>
+        <v>0.0110479176955577</v>
       </c>
       <c r="H29" t="n">
         <v>0.01255983518005343</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03575897593734056</v>
+        <v>0.05119794786423736</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0020663242761834</v>
+        <v>0.0048702402578796</v>
       </c>
       <c r="K29" t="n">
         <v>1.216464585690249e-05</v>
@@ -1197,11 +1213,19 @@
       <c r="E30" t="n">
         <v>0.00198797815895357</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.0377892534040361</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0103941771502339</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0239144387460175</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0028637068563015</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1440,17 +1464,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2050</v>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.006518820299633993</v>
-      </c>
+      <c r="D40" t="n">
+        <v>2.046363078989088e-19</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1461,17 +1485,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2050</v>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="n">
-        <v>2.046363078989088e-19</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.006518820299633993</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1519,19 +1543,19 @@
         <v>0.03359559287556831</v>
       </c>
       <c r="F43" t="n">
-        <v>0.006659924611096365</v>
+        <v>0.04444917801513246</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001897388056807923</v>
+        <v>0.01229156520704182</v>
       </c>
       <c r="H43" t="n">
         <v>0.01201612500046017</v>
       </c>
       <c r="I43" t="n">
-        <v>0.007400808941392975</v>
+        <v>0.03131524768741047</v>
       </c>
       <c r="J43" t="n">
-        <v>0.001940725930003292</v>
+        <v>0.004804432786304791</v>
       </c>
       <c r="K43" t="n">
         <v>1.111055925579658e-05</v>
